--- a/selenium-tests/reports/excel/Test_Report.xlsx
+++ b/selenium-tests/reports/excel/Test_Report.xlsx
@@ -61,7 +61,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>6/8/2026, 5:08:49 pm</t>
+    <t>6/8/2026, 5:16:58 pm</t>
   </si>
   <si>
     <t>reports/screenshots/TC-01_pass.png</t>
